--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_10_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_10_7.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_0</t>
+          <t>model_10_7_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9996339616364968</v>
+        <v>0.999637086508715</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7236562516705627</v>
+        <v>0.5261360028273459</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9991399707728065</v>
+        <v>0.9991257230804996</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9998821331001149</v>
+        <v>0.998723094346239</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9996664123088042</v>
+        <v>0.9992865200214457</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002172961846094816</v>
+        <v>0.000215441125473346</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1640495864367098</v>
+        <v>0.2813061385805167</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002724803720041416</v>
+        <v>0.0007829932527686401</v>
       </c>
       <c r="J2" t="n">
-        <v>1.754242428980095e-05</v>
+        <v>0.0004918910087592808</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000145011897995877</v>
+        <v>0.0006374418294469605</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004860433067093748</v>
+        <v>0.006877184064257914</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01474096959529737</v>
+        <v>0.01467791284458884</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000144015093837</v>
+        <v>1.000142785635916</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01536852318898293</v>
+        <v>0.01530278198185126</v>
       </c>
       <c r="P2" t="n">
-        <v>186.8684984580537</v>
+        <v>186.8856457708119</v>
       </c>
       <c r="Q2" t="n">
-        <v>290.4729435718507</v>
+        <v>290.4900908846089</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_1</t>
+          <t>model_10_7_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9996645446299778</v>
+        <v>0.9996426377518832</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7234416553524547</v>
+        <v>0.5259108842446187</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9991512995544845</v>
+        <v>0.9991413108407717</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999230737784445</v>
+        <v>0.9987603965572518</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9996775500476622</v>
+        <v>0.9993023746159854</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0001991407985626713</v>
+        <v>0.0002121456677274464</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1641769800812169</v>
+        <v>0.2814397786958399</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002688911095135869</v>
+        <v>0.000769033017920163</v>
       </c>
       <c r="J3" t="n">
-        <v>1.144912116000225e-05</v>
+        <v>0.0004775214097602934</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001401702785542369</v>
+        <v>0.0006232769165520056</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004646202085311397</v>
+        <v>0.006841581020651314</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01411172556998864</v>
+        <v>0.01456522116987746</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000131982440664</v>
+        <v>1.000140601540243</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0147124909428021</v>
+        <v>0.01518529278924349</v>
       </c>
       <c r="P3" t="n">
-        <v>187.0429969059116</v>
+        <v>186.9164748146473</v>
       </c>
       <c r="Q3" t="n">
-        <v>290.6474420197086</v>
+        <v>290.5209199284444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_2</t>
+          <t>model_10_7_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9996907588720564</v>
+        <v>0.9996482012242989</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7232262820762624</v>
+        <v>0.525673265476699</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9991543637841174</v>
+        <v>0.9991573314748643</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999403718319524</v>
+        <v>0.9987989618015528</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9996816283046613</v>
+        <v>0.9993187184639439</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001835788920685047</v>
+        <v>0.0002088429501719972</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1643048349616058</v>
+        <v>0.2815808394610734</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002679202792163338</v>
+        <v>0.0007546851058116198</v>
       </c>
       <c r="J4" t="n">
-        <v>8.874608770866843e-06</v>
+        <v>0.0004626652636805966</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001383974439936003</v>
+        <v>0.0006086748917495638</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004442841065021979</v>
+        <v>0.006804511827505212</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01354912883061139</v>
+        <v>0.01445139959215014</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000121668640502</v>
+        <v>1.000138412633063</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01412594329549376</v>
+        <v>0.01506662559130918</v>
       </c>
       <c r="P4" t="n">
-        <v>187.2057321066684</v>
+        <v>186.9478560461034</v>
       </c>
       <c r="Q4" t="n">
-        <v>290.8101772204655</v>
+        <v>290.5523011599004</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_3</t>
+          <t>model_10_7_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9997130726304484</v>
+        <v>0.9996537352352739</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7230118260887954</v>
+        <v>0.5254225202550806</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9991499982342305</v>
+        <v>0.9991737161217809</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999372919031603</v>
+        <v>0.9988388119616128</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9996795089019911</v>
+        <v>0.9993355217690348</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001703324811828024</v>
+        <v>0.0002055577222003967</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1644321452997825</v>
+        <v>0.2817296926562556</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002693034027423436</v>
+        <v>0.0007400111876302005</v>
       </c>
       <c r="J5" t="n">
-        <v>9.333002244407168e-06</v>
+        <v>0.0004473141409305167</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001393187567756306</v>
+        <v>0.000593662375827735</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004249763757004575</v>
+        <v>0.006765894072820347</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01305114865377</v>
+        <v>0.0143372843384093</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000112889456873</v>
+        <v>1.000136235317269</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01360676307156316</v>
+        <v>0.01494765221496546</v>
       </c>
       <c r="P5" t="n">
-        <v>187.3555165185638</v>
+        <v>186.9795673536986</v>
       </c>
       <c r="Q5" t="n">
-        <v>290.9599616323608</v>
+        <v>290.5840124674957</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_4</t>
+          <t>model_10_7_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9997319027049543</v>
+        <v>0.9996592214676736</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7227992523448299</v>
+        <v>0.5251577656478481</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9991390098497598</v>
+        <v>0.9991905053995942</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999166927760088</v>
+        <v>0.9988799234871112</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9996719769853685</v>
+        <v>0.9993527994948456</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001591541355393008</v>
+        <v>0.0002023008576550455</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1645583382569081</v>
+        <v>0.2818868624279124</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002727848182496531</v>
+        <v>0.000724974886255289</v>
       </c>
       <c r="J6" t="n">
-        <v>1.239882164613775e-05</v>
+        <v>0.0004314771135906975</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001425929109300259</v>
+        <v>0.0005782259999229932</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004081149348542001</v>
+        <v>0.006725441951148281</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01261563060410778</v>
+        <v>0.01422325060086637</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000105480902969</v>
+        <v>1.000134076799604</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01315270411688017</v>
+        <v>0.01482876382513294</v>
       </c>
       <c r="P6" t="n">
-        <v>187.4912748388139</v>
+        <v>187.0115091485576</v>
       </c>
       <c r="Q6" t="n">
-        <v>291.095719952611</v>
+        <v>290.6159542623547</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_5</t>
+          <t>model_10_7_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.999747627294987</v>
+        <v>0.9996646143258354</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7225893517617223</v>
+        <v>0.5248782906316245</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9991220936815927</v>
+        <v>0.9992076311690367</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9998811898512032</v>
+        <v>0.9989222821869063</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9996597360374843</v>
+        <v>0.9993705150704727</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001498193396289183</v>
+        <v>0.0001990994240908676</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1646829443102738</v>
+        <v>0.2820527708702348</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002781443149380312</v>
+        <v>0.0007096372265014562</v>
       </c>
       <c r="J7" t="n">
-        <v>1.768281037475572e-05</v>
+        <v>0.0004151596483883423</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001479140997293036</v>
+        <v>0.0005623984374448993</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00399854049285461</v>
+        <v>0.006683419828813719</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01224007106306652</v>
+        <v>0.01411025953307974</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000099294179021</v>
+        <v>1.000131955019343</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01276115622866135</v>
+        <v>0.01471096249366687</v>
       </c>
       <c r="P7" t="n">
-        <v>187.6121607844349</v>
+        <v>187.043412478921</v>
       </c>
       <c r="Q7" t="n">
-        <v>291.2166058982319</v>
+        <v>290.6478575927181</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_6</t>
+          <t>model_10_7_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9997605988451741</v>
+        <v>0.9996698693030396</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7223826650158782</v>
+        <v>0.5245832194776219</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9991000123206459</v>
+        <v>0.9992250831617903</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9998330168649675</v>
+        <v>0.9989658224336011</v>
       </c>
       <c r="F8" t="n">
-        <v>0.999643446816135</v>
+        <v>0.9993886488780926</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001421188670960566</v>
+        <v>0.0001959798426192889</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1648056424910094</v>
+        <v>0.2822279378536609</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002851402835108035</v>
+        <v>0.0006940074045667586</v>
       </c>
       <c r="J8" t="n">
-        <v>2.485251590426157e-05</v>
+        <v>0.0003983870263819404</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001549950891275053</v>
+        <v>0.0005461972154743495</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003929789588071312</v>
+        <v>0.006639592134765468</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01192136179704553</v>
+        <v>0.01399928007503561</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000094190618292</v>
+        <v>1.000129887487329</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01242887884936672</v>
+        <v>0.01459525841033465</v>
       </c>
       <c r="P8" t="n">
-        <v>187.7176935166071</v>
+        <v>187.0749974956034</v>
       </c>
       <c r="Q8" t="n">
-        <v>291.3221386304042</v>
+        <v>290.6794426094004</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_7</t>
+          <t>model_10_7_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9997711232599694</v>
+        <v>0.9996749456038694</v>
       </c>
       <c r="C9" t="n">
-        <v>0.722180390037512</v>
+        <v>0.5242715714581779</v>
       </c>
       <c r="D9" t="n">
-        <v>0.999073363307735</v>
+        <v>0.9992428298847293</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9997742044546509</v>
+        <v>0.9990105452236746</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9996236632562385</v>
+        <v>0.9994071853478446</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001358711198425358</v>
+        <v>0.0001929663311619383</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1649257216559916</v>
+        <v>0.2824129455804963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002935834069790929</v>
+        <v>0.0006781136253645998</v>
       </c>
       <c r="J9" t="n">
-        <v>3.360571342015477e-05</v>
+        <v>0.0003811588637068135</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001635950814096674</v>
+        <v>0.0005296362445357066</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00386467885064239</v>
+        <v>0.006593810786106956</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01165637678880259</v>
+        <v>0.01389123216859967</v>
       </c>
       <c r="N9" t="n">
-        <v>1.00009004986493</v>
+        <v>1.000127890254215</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0121526128807283</v>
+        <v>0.01448261068083174</v>
       </c>
       <c r="P9" t="n">
-        <v>187.8076075394946</v>
+        <v>187.1059896684314</v>
       </c>
       <c r="Q9" t="n">
-        <v>291.4120526532917</v>
+        <v>290.7104347822284</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_8</t>
+          <t>model_10_7_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9997794818912275</v>
+        <v>0.9996797760494699</v>
       </c>
       <c r="C10" t="n">
-        <v>0.721982752903457</v>
+        <v>0.5239424682969325</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9990427699930926</v>
+        <v>0.999260795909129</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9997065433942078</v>
+        <v>0.9990564150201022</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9996009334236485</v>
+        <v>0.999426079012754</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001309090752536638</v>
+        <v>0.0001900987699890375</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1650430475962463</v>
+        <v>0.2826083154335279</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003032761912369059</v>
+        <v>0.0006620234420711781</v>
       </c>
       <c r="J10" t="n">
-        <v>4.367587757436107e-05</v>
+        <v>0.0003634888499748493</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0001734758301662632</v>
+        <v>0.0005127561460230137</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003803016973495884</v>
+        <v>0.006546248168377066</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01144155038679915</v>
+        <v>0.01378763105065687</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000086761223124</v>
+        <v>1.000125989751028</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01192864087403961</v>
+        <v>0.01437459904881424</v>
       </c>
       <c r="P10" t="n">
-        <v>187.8820151155653</v>
+        <v>187.1359335576546</v>
       </c>
       <c r="Q10" t="n">
-        <v>291.4864602293624</v>
+        <v>290.7403786714517</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_9</t>
+          <t>model_10_7_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9997859264674525</v>
+        <v>0.9996842968282087</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7217902040267306</v>
+        <v>0.5235948398255184</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9990087165969138</v>
+        <v>0.9992789515846376</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9996316298239684</v>
+        <v>0.9991032805602154</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9995756989955414</v>
+        <v>0.9994452832553182</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001270832964153382</v>
+        <v>0.0001874150404422157</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1651573529271495</v>
+        <v>0.2828146827109274</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0003140652223133116</v>
+        <v>0.0006457634092306688</v>
       </c>
       <c r="J11" t="n">
-        <v>5.482545082592923e-05</v>
+        <v>0.0003454352547586453</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0001844453365696204</v>
+        <v>0.0004955985692427099</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003744536152894608</v>
+        <v>0.006496836765200723</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01127312274462308</v>
+        <v>0.01368996130170629</v>
       </c>
       <c r="N11" t="n">
-        <v>1.00008422565215</v>
+        <v>1.000124211083983</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01175304291844282</v>
+        <v>0.01427277129644658</v>
       </c>
       <c r="P11" t="n">
-        <v>187.9413356184261</v>
+        <v>187.1643698657683</v>
       </c>
       <c r="Q11" t="n">
-        <v>291.5457807322232</v>
+        <v>290.7688149795653</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_10</t>
+          <t>model_10_7_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.999790685798753</v>
+        <v>0.9996884360876345</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7216033663046647</v>
+        <v>0.5232274918589288</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9989717790233816</v>
+        <v>0.9992972305203989</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9995508072964782</v>
+        <v>0.9991511183474973</v>
       </c>
       <c r="F12" t="n">
-        <v>0.999548400790004</v>
+        <v>0.9994647553595715</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001242579517629201</v>
+        <v>0.0001849577972404319</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1652682678699371</v>
+        <v>0.2830327563325009</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0003257680382859884</v>
+        <v>0.0006293929857989211</v>
       </c>
       <c r="J12" t="n">
-        <v>6.685446890301077e-05</v>
+        <v>0.0003270071294123779</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0001963119752416887</v>
+        <v>0.0004782016777650662</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003689356041208214</v>
+        <v>0.006445456894824595</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01114710508441183</v>
+        <v>0.01359991901595123</v>
       </c>
       <c r="N12" t="n">
-        <v>1.00008235312836</v>
+        <v>1.000122582522898</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01162166042554386</v>
+        <v>0.0141788957241737</v>
       </c>
       <c r="P12" t="n">
-        <v>187.9863017938868</v>
+        <v>187.1907657638693</v>
       </c>
       <c r="Q12" t="n">
-        <v>291.5907469076839</v>
+        <v>290.7952108776664</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_11</t>
+          <t>model_10_7_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.99979396607586</v>
+        <v>0.9996921124521935</v>
       </c>
       <c r="C13" t="n">
-        <v>0.721422042619386</v>
+        <v>0.5228393121422394</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9989324031776866</v>
+        <v>0.9993155654006057</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9994653686456965</v>
+        <v>0.9991997970062645</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9995194264957126</v>
+        <v>0.9994844412647919</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001223106375716128</v>
+        <v>0.0001827753484275166</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1653759094422939</v>
+        <v>0.2832631965808183</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0003382433644071387</v>
+        <v>0.0006129724591075374</v>
       </c>
       <c r="J13" t="n">
-        <v>7.957051610729026e-05</v>
+        <v>0.0003082550826220911</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0002089072163707141</v>
+        <v>0.0004606137708648142</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003662382993908432</v>
+        <v>0.006392159802644748</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01105941397957472</v>
+        <v>0.0135194433475464</v>
       </c>
       <c r="N13" t="n">
-        <v>1.00008106252753</v>
+        <v>1.000121136084383</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01153023612882822</v>
+        <v>0.01409499403995727</v>
       </c>
       <c r="P13" t="n">
-        <v>188.0178930794546</v>
+        <v>187.2145055269347</v>
       </c>
       <c r="Q13" t="n">
-        <v>291.6223381932516</v>
+        <v>290.8189506407318</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9997959571763304</v>
+        <v>0.9996952314032357</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7212469203625714</v>
+        <v>0.5224290873195914</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9988910576880802</v>
+        <v>0.9993338544236452</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9993763408254862</v>
+        <v>0.9992492158938836</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9994891197993232</v>
+        <v>0.9995042616967084</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001211286343212765</v>
+        <v>0.0001809238043571705</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1654798695788267</v>
+        <v>0.2835067237563318</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0003513427266525497</v>
+        <v>0.0005965930016150924</v>
       </c>
       <c r="J14" t="n">
-        <v>9.282074833744349e-05</v>
+        <v>0.0002892178840545044</v>
       </c>
       <c r="K14" t="n">
-        <v>0.000222081657998509</v>
+        <v>0.0004429056742663675</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003637266224166754</v>
+        <v>0.00633690868237356</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01100584546144804</v>
+        <v>0.01345079196022191</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000080279143739</v>
+        <v>1.000119908956104</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01147438708798277</v>
+        <v>0.01402342002094642</v>
       </c>
       <c r="P14" t="n">
-        <v>188.0373149669741</v>
+        <v>187.2348691714675</v>
       </c>
       <c r="Q14" t="n">
-        <v>291.6417600807712</v>
+        <v>290.8393142852645</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_13</t>
+          <t>model_10_7_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9997968205745965</v>
+        <v>0.9996977015772162</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7210778295349581</v>
+        <v>0.521995476187336</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9988480865583277</v>
+        <v>0.9993520522527799</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9992847288388744</v>
+        <v>0.9992992666155889</v>
       </c>
       <c r="F15" t="n">
-        <v>0.999457779403885</v>
+        <v>0.9995241724063308</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001206160838136665</v>
+        <v>0.0001794574023763851</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1655802491984413</v>
+        <v>0.2837641340554642</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0003649571353844699</v>
+        <v>0.000580295216428599</v>
       </c>
       <c r="J15" t="n">
-        <v>0.000106455588489693</v>
+        <v>0.0002699372896611665</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0002357054527198546</v>
+        <v>0.000425116921184512</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003613582351257639</v>
+        <v>0.006279477626995562</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01098253540006434</v>
+        <v>0.01339617118345332</v>
       </c>
       <c r="N15" t="n">
-        <v>1.00007993944606</v>
+        <v>1.000118937084374</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01145008466902749</v>
+        <v>0.0139664739246302</v>
       </c>
       <c r="P15" t="n">
-        <v>188.0457958352155</v>
+        <v>187.2511453817309</v>
       </c>
       <c r="Q15" t="n">
-        <v>291.6502409490125</v>
+        <v>290.8555904955279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_14</t>
+          <t>model_10_7_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.999796707445995</v>
+        <v>0.9996993876206837</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7209150521179966</v>
+        <v>0.5215370639057549</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9988038792885662</v>
+        <v>0.9993700140601408</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9991912575710292</v>
+        <v>0.9993497150027397</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9994256661918997</v>
+        <v>0.9995440517872327</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001206832418384371</v>
+        <v>0.0001784564941408307</v>
       </c>
       <c r="H16" t="n">
-        <v>0.165676880904768</v>
+        <v>0.2840362673881902</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0003789631864918308</v>
+        <v>0.0005642088098708443</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001203671500989789</v>
+        <v>0.0002505035061448992</v>
       </c>
       <c r="K16" t="n">
-        <v>0.000249665193872357</v>
+        <v>0.0004073561580078717</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003591096961383009</v>
+        <v>0.006220326923270552</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01098559246642788</v>
+        <v>0.01335876095080793</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000079983955674</v>
+        <v>1.00011827372301</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01145327188103513</v>
+        <v>0.01392747106093123</v>
       </c>
       <c r="P16" t="n">
-        <v>188.0446825618762</v>
+        <v>187.2623314335102</v>
       </c>
       <c r="Q16" t="n">
-        <v>291.6491276756733</v>
+        <v>290.8667765473073</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_15</t>
+          <t>model_10_7_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9997957421965692</v>
+        <v>0.9997001762143163</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7207582163670918</v>
+        <v>0.521052557554471</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9987586631429466</v>
+        <v>0.999387655459644</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9990966980264531</v>
+        <v>0.9994004501595425</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9993930001609806</v>
+        <v>0.9995638316521119</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001212562555942214</v>
+        <v>0.0001779883508949927</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1657699853814567</v>
+        <v>0.2843238912878969</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000393288876584031</v>
+        <v>0.0005484093572348763</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0001344406826447654</v>
+        <v>0.0002309592529060089</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0002638652476170691</v>
+        <v>0.0003896843050704425</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003569933831092248</v>
+        <v>0.006159059390283451</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01101164182101022</v>
+        <v>0.01334122748831579</v>
       </c>
       <c r="N17" t="n">
-        <v>1.00008036372594</v>
+        <v>1.000117963456662</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01148043021057163</v>
+        <v>0.01390919116264153</v>
       </c>
       <c r="P17" t="n">
-        <v>188.0352088738957</v>
+        <v>187.2675849084478</v>
       </c>
       <c r="Q17" t="n">
-        <v>291.6396539876928</v>
+        <v>290.8720300222449</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_16</t>
+          <t>model_10_7_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9997940586392985</v>
+        <v>0.9996999169657287</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7206075688903015</v>
+        <v>0.5205402984101242</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9987128656064088</v>
+        <v>0.9994048404006947</v>
       </c>
       <c r="E18" t="n">
-        <v>0.999001655867114</v>
+        <v>0.9994511948152021</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9993600427504729</v>
+        <v>0.999583384783003</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001222556879159975</v>
+        <v>0.000178142252055576</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1658594162313116</v>
+        <v>0.284627990444424</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0004077987669436989</v>
+        <v>0.0005330187040084143</v>
       </c>
       <c r="J18" t="n">
-        <v>0.000148586043947825</v>
+        <v>0.0002114113405069849</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0002781919652295186</v>
+        <v>0.0003722150222576996</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003549986862065786</v>
+        <v>0.00609590511327642</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01105692940720874</v>
+        <v>0.01334699412060918</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000081026109128</v>
+        <v>1.000118065456107</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01152764578307285</v>
+        <v>0.01391520329241023</v>
       </c>
       <c r="P18" t="n">
-        <v>188.0187918075428</v>
+        <v>187.2658563159721</v>
       </c>
       <c r="Q18" t="n">
-        <v>291.6232369213399</v>
+        <v>290.8703014297691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_17</t>
+          <t>model_10_7_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9997917597151468</v>
+        <v>0.9996984500276699</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7204631638444958</v>
+        <v>0.5199984544812468</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9986667246701224</v>
+        <v>0.999421421336957</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9989066818922717</v>
+        <v>0.9995017165759197</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9993269709849598</v>
+        <v>0.9996025875325687</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00012362042860082</v>
+        <v>0.0001790130898557007</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1659451413044751</v>
+        <v>0.2849496524070446</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0004224174555724382</v>
+        <v>0.0005181689911446898</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0001627212571823797</v>
+        <v>0.0001919492919441313</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0002925683934182823</v>
+        <v>0.0003550587793616253</v>
       </c>
       <c r="L19" t="n">
-        <v>0.003531152715566134</v>
+        <v>0.006030753047627703</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0111184724041039</v>
+        <v>0.01337957734219212</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000081930603877</v>
+        <v>1.000118642612064</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0115918087927574</v>
+        <v>0.01394917364919251</v>
       </c>
       <c r="P19" t="n">
-        <v>187.996589493312</v>
+        <v>187.2561032542235</v>
       </c>
       <c r="Q19" t="n">
-        <v>291.6010346071091</v>
+        <v>290.8605483680205</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_18</t>
+          <t>model_10_7_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9997889383981061</v>
+        <v>0.9996955928695715</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7203247019603634</v>
+        <v>0.5194254519023371</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9986204214953699</v>
+        <v>0.9994372592065928</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9988122891367957</v>
+        <v>0.9995517468499745</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9992939361772583</v>
+        <v>0.9996213110806682</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001252952842706866</v>
+        <v>0.0001807092223256538</v>
       </c>
       <c r="H20" t="n">
-        <v>0.166027338260138</v>
+        <v>0.285289811490308</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0004370875457072967</v>
+        <v>0.0005039847609695439</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0001767699660909832</v>
+        <v>0.0001726765744173043</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00030692875589914</v>
+        <v>0.0003383306676934241</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0035133423089433</v>
+        <v>0.005963788851167572</v>
       </c>
       <c r="M20" t="n">
-        <v>0.01119353761197445</v>
+        <v>0.01344281303617862</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000083040630253</v>
+        <v>1.000119766739841</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0116700696819334</v>
+        <v>0.01401510141758795</v>
       </c>
       <c r="P20" t="n">
-        <v>187.9696746645595</v>
+        <v>187.2372426500037</v>
       </c>
       <c r="Q20" t="n">
-        <v>291.5741197783566</v>
+        <v>290.8416877638007</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_19</t>
+          <t>model_10_7_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9997856795040247</v>
+        <v>0.9996911661678203</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7201920155003045</v>
+        <v>0.5188192969724028</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9985741910411846</v>
+        <v>0.999452211318352</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9987187137895566</v>
+        <v>0.999600976528941</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9992610747554118</v>
+        <v>0.9996394179601671</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001272299045742748</v>
+        <v>0.0001833371037087871</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1661061066745855</v>
+        <v>0.2856496512412465</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0004517345960121248</v>
+        <v>0.0004905938062719821</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0001906970180956858</v>
+        <v>0.0001537122630162613</v>
       </c>
       <c r="K21" t="n">
-        <v>0.000321213746858252</v>
+        <v>0.0003221535040164032</v>
       </c>
       <c r="L21" t="n">
-        <v>0.003496566255493887</v>
+        <v>0.0058948285897324</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01127962342342486</v>
+        <v>0.01354020323735161</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000084322818089</v>
+        <v>1.000121508392989</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01175982034459945</v>
+        <v>0.01411663772125039</v>
       </c>
       <c r="P21" t="n">
-        <v>187.9390296716706</v>
+        <v>187.2083680058661</v>
       </c>
       <c r="Q21" t="n">
-        <v>291.5434747854677</v>
+        <v>290.8128131196631</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_20</t>
+          <t>model_10_7_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9997820606108756</v>
+        <v>0.9996849370590951</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7200652849051863</v>
+        <v>0.5181781123847717</v>
       </c>
       <c r="D22" t="n">
-        <v>0.998528212322667</v>
+        <v>0.9994660332978919</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9986263937396965</v>
+        <v>0.9996490614692677</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9992285079426235</v>
+        <v>0.9996567113718836</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001293782358756575</v>
+        <v>0.0001870349717315216</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1661813394303244</v>
+        <v>0.2860302861101963</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0004663018896921648</v>
+        <v>0.0004782149861542399</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0002044372410648043</v>
+        <v>0.0001351889291005459</v>
       </c>
       <c r="K22" t="n">
-        <v>0.000335370670086368</v>
+        <v>0.0003067031139096793</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003484245481830505</v>
+        <v>0.005824233380620293</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01137445541006942</v>
+        <v>0.01367607296454365</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000085746644901</v>
+        <v>1.000123959189864</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01185868952524475</v>
+        <v>0.0142582917040181</v>
       </c>
       <c r="P22" t="n">
-        <v>187.9055407653163</v>
+        <v>187.1684298879753</v>
       </c>
       <c r="Q22" t="n">
-        <v>291.5099858791133</v>
+        <v>290.7728750017724</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_21</t>
+          <t>model_10_7_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9997781441896023</v>
+        <v>0.9996766681579786</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7199441648043675</v>
+        <v>0.5174997777236003</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9984826510002821</v>
+        <v>0.9994785729860463</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9985355361207205</v>
+        <v>0.9996955998539769</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9991963497903277</v>
+        <v>0.9996730310127896</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001317031927240339</v>
+        <v>0.0001919437486321968</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1662532415542864</v>
+        <v>0.2864329748675993</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0004807369410600553</v>
+        <v>0.0004669845727717308</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0002179598068028773</v>
+        <v>0.0001172613610510258</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0003493499469708029</v>
+        <v>0.0002921227163264351</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003481410719103206</v>
+        <v>0.005751952305805346</v>
       </c>
       <c r="M23" t="n">
-        <v>0.011476201145154</v>
+        <v>0.01385437651546243</v>
       </c>
       <c r="N23" t="n">
-        <v>1.00008728753196</v>
+        <v>1.000127212528009</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01196476678691458</v>
+        <v>0.01444418600623873</v>
       </c>
       <c r="P23" t="n">
-        <v>187.8699194142185</v>
+        <v>187.1166164094726</v>
       </c>
       <c r="Q23" t="n">
-        <v>291.4743645280155</v>
+        <v>290.7210615232696</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_22</t>
+          <t>model_10_7_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.999773999535587</v>
+        <v>0.9996661044385454</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7198284741513379</v>
+        <v>0.5167821687325298</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9984376867806946</v>
+        <v>0.9994896115108777</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9984464603189651</v>
+        <v>0.9997401978007032</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9991647189546284</v>
+        <v>0.9996881769905253</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0001341636383872849</v>
+        <v>0.0001982148288166771</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1663219205235008</v>
+        <v>0.2868589785637931</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0004949828142149463</v>
+        <v>0.0004570985855396358</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0002312171802458894</v>
+        <v>0.0001000812906682433</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0003630999972304178</v>
+        <v>0.0002785909003725319</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00347866083079921</v>
+        <v>0.005678113245240145</v>
       </c>
       <c r="M24" t="n">
-        <v>0.01158290284804655</v>
+        <v>0.01407887881958919</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000088918215507</v>
+        <v>1.00013136874549</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01207601100220225</v>
+        <v>0.014678245838236</v>
       </c>
       <c r="P24" t="n">
-        <v>187.8329006421099</v>
+        <v>187.0523182428535</v>
       </c>
       <c r="Q24" t="n">
-        <v>291.437345755907</v>
+        <v>290.6567633566505</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_23</t>
+          <t>model_10_7_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.999769664003588</v>
+        <v>0.9996529506647104</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7197178469025547</v>
+        <v>0.5160230033956599</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9983933100699277</v>
+        <v>0.9994989113565401</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9983593233150064</v>
+        <v>0.9997823769422973</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9991336295059455</v>
+        <v>0.9997019324969951</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001367373974671299</v>
+        <v>0.0002060234771785645</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1663875936372268</v>
+        <v>0.2873096519019941</v>
       </c>
       <c r="I25" t="n">
-        <v>0.000509042548786454</v>
+        <v>0.0004487697411620313</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0002441859975837233</v>
+        <v>8.383299507473413e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0003766147043977893</v>
+        <v>0.0002663013681183828</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003476193018452205</v>
+        <v>0.005608186514477279</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01169347670571631</v>
+        <v>0.01435351793737565</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000090623998588</v>
+        <v>1.00013654400077</v>
       </c>
       <c r="O25" t="n">
-        <v>0.01219129221791244</v>
+        <v>0.01496457691184798</v>
       </c>
       <c r="P25" t="n">
-        <v>187.794896556741</v>
+        <v>186.9750408575644</v>
       </c>
       <c r="Q25" t="n">
-        <v>291.3993416705381</v>
+        <v>290.5794859713615</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_10_7_24</t>
+          <t>model_10_7_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9997651974308859</v>
+        <v>0.9996368862428141</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7196122856030278</v>
+        <v>0.5152197695415772</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9983497670846325</v>
+        <v>0.9995061989146555</v>
       </c>
       <c r="E26" t="n">
-        <v>0.998274344008111</v>
+        <v>0.9998216395470813</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9991032166310835</v>
+        <v>0.9997140486666062</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0001393889479690129</v>
+        <v>0.0002155600119631062</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1664502593846366</v>
+        <v>0.2877864862156733</v>
       </c>
       <c r="I26" t="n">
-        <v>0.000522838136722593</v>
+        <v>0.0004422430804367239</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0002568336794932791</v>
+        <v>6.870821101822888e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0003898353022305863</v>
+        <v>0.0002554764626481413</v>
       </c>
       <c r="L26" t="n">
-        <v>0.003473851864254754</v>
+        <v>0.005546474426155473</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01180630966767402</v>
+        <v>0.01468196212919466</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000092381338668</v>
+        <v>1.000142864429057</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01230892871265712</v>
+        <v>0.01530700365288593</v>
       </c>
       <c r="P26" t="n">
-        <v>187.7564846912861</v>
+        <v>186.8845424188024</v>
       </c>
       <c r="Q26" t="n">
-        <v>291.3609298050832</v>
+        <v>290.4889875325994</v>
       </c>
     </row>
   </sheetData>
